--- a/artfynd/A 12632-2025 artfynd.xlsx
+++ b/artfynd/A 12632-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133218064</v>
+        <v>133218065</v>
       </c>
       <c r="B2" t="n">
-        <v>79333</v>
+        <v>97995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585088</v>
+        <v>585133</v>
       </c>
       <c r="R2" t="n">
-        <v>7009515</v>
+        <v>7009507</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133218065</v>
+        <v>133218064</v>
       </c>
       <c r="B3" t="n">
-        <v>97995</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585133</v>
+        <v>585088</v>
       </c>
       <c r="R3" t="n">
-        <v>7009507</v>
+        <v>7009515</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 12632-2025 artfynd.xlsx
+++ b/artfynd/A 12632-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133218065</v>
+        <v>133218064</v>
       </c>
       <c r="B2" t="n">
-        <v>97995</v>
+        <v>79333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585133</v>
+        <v>585088</v>
       </c>
       <c r="R2" t="n">
-        <v>7009507</v>
+        <v>7009515</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133218064</v>
+        <v>133218065</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>97995</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585088</v>
+        <v>585133</v>
       </c>
       <c r="R3" t="n">
-        <v>7009515</v>
+        <v>7009507</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
